--- a/scripts/inputs_qserver_kafka_v2.xlsx
+++ b/scripts/inputs_qserver_kafka_v2.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="812" uniqueCount="194">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="814" uniqueCount="196">
   <si>
     <t xml:space="preserve">Input parameters for tasks in queue server</t>
   </si>
@@ -427,6 +427,12 @@
   </si>
   <si>
     <t xml:space="preserve">noisy_det</t>
+  </si>
+  <si>
+    <t xml:space="preserve">http_server_uri</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://xf28id2-xpd-qs1.nsls2.bnl.gov:443</t>
   </si>
   <si>
     <t xml:space="preserve">OLA</t>
@@ -822,7 +828,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="22">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -900,10 +906,6 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -994,7 +996,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:I54"/>
-  <sheetFormatPr defaultColWidth="12.046875" defaultRowHeight="13" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="12.06640625" defaultRowHeight="13" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="40.5"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="0" width="17.83"/>
@@ -1481,7 +1483,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:C47"/>
-  <sheetFormatPr defaultColWidth="12.046875" defaultRowHeight="13" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="12.06640625" defaultRowHeight="13" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="40.5"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="0" width="78.65"/>
@@ -1492,16 +1494,16 @@
       <c r="A1" s="0" t="s">
         <v>60</v>
       </c>
-      <c r="B1" s="22" t="s">
-        <v>154</v>
+      <c r="B1" s="21" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="0" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="C2" s="0" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1509,7 +1511,7 @@
         <v>61</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1517,7 +1519,7 @@
         <v>62</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1525,7 +1527,7 @@
         <v>64</v>
       </c>
       <c r="B5" s="0" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1533,7 +1535,7 @@
         <v>65</v>
       </c>
       <c r="B6" s="0" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1541,7 +1543,7 @@
         <v>66</v>
       </c>
       <c r="B7" s="0" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1549,12 +1551,12 @@
         <v>67</v>
       </c>
       <c r="B8" s="0" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="0" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1562,7 +1564,7 @@
         <v>69</v>
       </c>
       <c r="B10" s="0" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1570,7 +1572,7 @@
         <v>72</v>
       </c>
       <c r="B11" s="0" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1578,12 +1580,12 @@
         <v>76</v>
       </c>
       <c r="B12" s="0" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="0" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1591,7 +1593,7 @@
         <v>77</v>
       </c>
       <c r="B14" s="0" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1599,7 +1601,7 @@
         <v>78</v>
       </c>
       <c r="B15" s="0" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1607,12 +1609,12 @@
         <v>79</v>
       </c>
       <c r="B16" s="0" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="0" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1620,7 +1622,7 @@
         <v>80</v>
       </c>
       <c r="B18" s="0" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1628,7 +1630,7 @@
         <v>81</v>
       </c>
       <c r="B19" s="0" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1636,12 +1638,12 @@
         <v>83</v>
       </c>
       <c r="B20" s="0" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="0" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1649,7 +1651,7 @@
         <v>84</v>
       </c>
       <c r="B22" s="0" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1764,7 +1766,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:H24"/>
-  <sheetFormatPr defaultColWidth="12.046875" defaultRowHeight="13" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="12.06640625" defaultRowHeight="13" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="40.5"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="24"/>
@@ -1774,12 +1776,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="0" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="B2" s="0" t="n">
         <v>0</v>
@@ -1790,7 +1792,7 @@
         <v>62</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1889,13 +1891,13 @@
         <v>23</v>
       </c>
       <c r="B9" s="0" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="C9" s="0" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="D9" s="0" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1945,10 +1947,10 @@
         <v>37</v>
       </c>
       <c r="B13" s="0" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="C13" s="0" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1959,12 +1961,12 @@
         <v>49</v>
       </c>
       <c r="C14" s="0" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="0" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="B15" s="0" t="n">
         <v>50</v>
@@ -1973,7 +1975,7 @@
         <v>46</v>
       </c>
       <c r="D15" s="0" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="E15" s="0" t="n">
         <v>300</v>
@@ -1992,13 +1994,13 @@
         <v>59</v>
       </c>
       <c r="B17" s="0" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="C17" s="0" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="D17" s="0" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2006,13 +2008,13 @@
         <v>59</v>
       </c>
       <c r="B18" s="0" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="C18" s="0" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="D18" s="0" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2020,13 +2022,13 @@
         <v>59</v>
       </c>
       <c r="B19" s="0" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="C19" s="0" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="D19" s="0" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2034,13 +2036,13 @@
         <v>59</v>
       </c>
       <c r="B20" s="0" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="C20" s="0" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="D20" s="0" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2116,7 +2118,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:I39"/>
-  <sheetFormatPr defaultColWidth="12.046875" defaultRowHeight="13" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="12.06640625" defaultRowHeight="13" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="40.5"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="0" width="17.83"/>
@@ -2127,12 +2129,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="0" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="B2" s="0" t="n">
         <v>0</v>
@@ -2146,7 +2148,7 @@
         <v>62</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2213,10 +2215,10 @@
         <v>13</v>
       </c>
       <c r="E8" s="0" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="F8" s="0" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G8" s="0" t="s">
         <v>16</v>
@@ -2239,7 +2241,7 @@
         <v>20</v>
       </c>
       <c r="F9" s="0" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2247,16 +2249,16 @@
         <v>23</v>
       </c>
       <c r="B10" s="0" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C10" s="0" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="D10" s="0" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="E10" s="0" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="F10" s="0" t="s">
         <v>28</v>
@@ -2310,7 +2312,7 @@
         <v>35</v>
       </c>
       <c r="C13" s="0" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="D13" s="0" t="s">
         <v>129</v>
@@ -2319,7 +2321,7 @@
         <v>35</v>
       </c>
       <c r="F13" s="0" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2347,12 +2349,12 @@
         <v>49</v>
       </c>
       <c r="C15" s="0" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="0" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="B16" s="0" t="n">
         <v>0</v>
@@ -2392,7 +2394,7 @@
     </row>
     <row r="18" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="0" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="B18" s="0" t="n">
         <v>36</v>
@@ -2839,7 +2841,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:H1048576"/>
-  <sheetFormatPr defaultColWidth="11.70703125" defaultRowHeight="13" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.72265625" defaultRowHeight="13" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="40.5"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="17.67"/>
@@ -3257,7 +3259,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:H47"/>
-  <sheetFormatPr defaultColWidth="11.70703125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.72265625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="40.5"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="17.67"/>
@@ -3855,7 +3857,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:G55"/>
-  <sheetFormatPr defaultColWidth="12.046875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="12.06640625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="40.5"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="0" width="17.83"/>
@@ -4756,8 +4758,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:J39"/>
-  <sheetFormatPr defaultColWidth="12.046875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:J40"/>
+  <sheetFormatPr defaultColWidth="12.06640625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="40.5"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="0" width="17.83"/>
@@ -4772,7 +4774,7 @@
       </c>
     </row>
     <row r="2" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="3" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
         <v>1</v>
       </c>
@@ -4788,408 +4790,391 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="6" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
-        <v>5</v>
-      </c>
-      <c r="B6" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="C6" s="0" t="n">
-        <v>5</v>
-      </c>
-    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="0" t="s">
+        <v>132</v>
+      </c>
+      <c r="B5" s="0" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="7" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B7" s="0" t="n">
         <v>0</v>
+      </c>
+      <c r="C7" s="0" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
+        <v>6</v>
+      </c>
+      <c r="B8" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="0" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="0" t="s">
+      <c r="B9" s="0" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="10" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="s">
-        <v>9</v>
-      </c>
-      <c r="B10" s="0" t="n">
-        <v>0</v>
-      </c>
-    </row>
+    <row r="10" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="11" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="s">
+        <v>9</v>
+      </c>
+      <c r="B11" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="0" t="s">
         <v>10</v>
       </c>
-      <c r="B11" s="0" t="n">
+      <c r="B12" s="0" t="n">
         <v>1</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="0" t="s">
-        <v>17</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="D13" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="E13" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="F13" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="G13" s="6" t="s">
-        <v>22</v>
+        <v>11</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="0" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>134</v>
+        <v>19</v>
       </c>
       <c r="D14" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E14" s="5" t="s">
         <v>135</v>
       </c>
-      <c r="E14" s="0" t="s">
-        <v>136</v>
-      </c>
       <c r="F14" s="5" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="0" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>30</v>
+        <v>136</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="E15" s="5" t="s">
-        <v>30</v>
+        <v>137</v>
+      </c>
+      <c r="E15" s="0" t="s">
+        <v>138</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="G15" s="6" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="0" t="s">
-        <v>32</v>
-      </c>
-      <c r="B16" s="4" t="n">
-        <v>50</v>
-      </c>
-      <c r="C16" s="5" t="n">
-        <v>50</v>
-      </c>
-      <c r="D16" s="5" t="n">
-        <v>50</v>
-      </c>
-      <c r="E16" s="5" t="n">
-        <v>50</v>
-      </c>
-      <c r="F16" s="5" t="n">
-        <v>20</v>
-      </c>
-      <c r="G16" s="6" t="n">
-        <v>100</v>
+        <v>29</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="F16" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="G16" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="B17" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="0" t="s">
         <v>33</v>
       </c>
-      <c r="B17" s="7" t="s">
-        <v>137</v>
-      </c>
-      <c r="C17" s="8" t="s">
-        <v>138</v>
-      </c>
-      <c r="D17" s="8" t="s">
-        <v>137</v>
-      </c>
-      <c r="E17" s="8" t="s">
-        <v>137</v>
-      </c>
-      <c r="F17" s="8" t="s">
+      <c r="B18" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="C18" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="D18" s="8" t="s">
+        <v>139</v>
+      </c>
+      <c r="E18" s="8" t="s">
+        <v>139</v>
+      </c>
+      <c r="F18" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="G17" s="9" t="s">
+      <c r="G18" s="9" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="19" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="0" t="s">
+    <row r="19" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="20" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="0" t="s">
         <v>37</v>
       </c>
-      <c r="B19" s="10" t="s">
+      <c r="B20" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="C19" s="10" t="s">
+      <c r="C20" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="D19" s="10" t="s">
+      <c r="D20" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="E19" s="10"/>
-      <c r="F19" s="10"/>
-      <c r="G19" s="10"/>
-    </row>
-    <row r="20" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B20" s="10"/>
-      <c r="C20" s="10"/>
-      <c r="D20" s="10"/>
       <c r="E20" s="10"/>
       <c r="F20" s="10"/>
       <c r="G20" s="10"/>
     </row>
-    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="0" t="s">
-        <v>41</v>
-      </c>
-      <c r="B21" s="10" t="n">
-        <v>20</v>
-      </c>
-      <c r="C21" s="10" t="n">
-        <v>2</v>
-      </c>
+    <row r="21" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B21" s="10"/>
+      <c r="C21" s="10"/>
       <c r="D21" s="10"/>
       <c r="E21" s="10"/>
       <c r="F21" s="10"/>
       <c r="G21" s="10"/>
     </row>
-    <row r="22" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="0" t="s">
-        <v>42</v>
-      </c>
-      <c r="B22" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="C22" s="0" t="n">
-        <v>240</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="B22" s="10" t="n">
+        <v>20</v>
+      </c>
+      <c r="C22" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="D22" s="10"/>
+      <c r="E22" s="10"/>
+      <c r="F22" s="10"/>
+      <c r="G22" s="10"/>
     </row>
     <row r="23" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="0" t="s">
+        <v>42</v>
+      </c>
+      <c r="B23" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="C23" s="0" t="n">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="0" t="s">
         <v>43</v>
       </c>
-      <c r="B23" s="0" t="n">
+      <c r="B24" s="0" t="n">
         <v>50</v>
       </c>
-      <c r="C23" s="0" t="s">
+      <c r="C24" s="0" t="s">
         <v>44</v>
       </c>
-      <c r="D23" s="0" t="s">
+      <c r="D24" s="0" t="s">
         <v>45</v>
       </c>
-      <c r="E23" s="0" t="n">
+      <c r="E24" s="0" t="n">
         <v>20</v>
       </c>
-      <c r="F23" s="0" t="s">
+      <c r="F24" s="0" t="s">
         <v>46</v>
       </c>
-      <c r="G23" s="0" t="s">
+      <c r="G24" s="0" t="s">
         <v>47</v>
       </c>
-      <c r="J23" s="0" t="n">
+      <c r="J24" s="0" t="n">
         <v>12</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="25" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="0" t="s">
-        <v>48</v>
-      </c>
-      <c r="B26" s="0" t="s">
-        <v>49</v>
-      </c>
-    </row>
+    <row r="26" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="0" t="s">
+        <v>48</v>
+      </c>
+      <c r="B27" s="0" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="0" t="s">
         <v>50</v>
       </c>
-      <c r="B27" s="0" t="n">
+      <c r="B28" s="0" t="n">
         <v>2.3</v>
       </c>
-      <c r="C27" s="0" t="n">
+      <c r="C28" s="0" t="n">
         <v>2.3</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="0" t="s">
+    <row r="29" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="0" t="s">
         <v>51</v>
       </c>
-      <c r="B28" s="0" t="s">
+      <c r="B29" s="0" t="s">
         <v>52</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="0" t="s">
-        <v>53</v>
-      </c>
-      <c r="B29" s="0" t="s">
-        <v>54</v>
-      </c>
-      <c r="C29" s="0" t="n">
-        <v>20</v>
-      </c>
-      <c r="D29" s="0" t="n">
-        <v>20</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="0" t="s">
+        <v>53</v>
+      </c>
+      <c r="B30" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="C30" s="0" t="n">
+        <v>20</v>
+      </c>
+      <c r="D30" s="0" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="0" t="s">
         <v>55</v>
       </c>
-      <c r="B30" s="0" t="s">
+      <c r="B31" s="0" t="s">
         <v>56</v>
       </c>
-      <c r="C30" s="0" t="n">
+      <c r="C31" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="D30" s="0" t="n">
+      <c r="D31" s="0" t="n">
         <v>600</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="32" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="0" t="s">
+    <row r="32" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="33" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="0" t="s">
         <v>57</v>
       </c>
-      <c r="B32" s="0" t="n">
+      <c r="B33" s="0" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="0" t="s">
+    <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="0" t="s">
         <v>58</v>
       </c>
-      <c r="B33" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="C33" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D33" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="E33" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="F33" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="G33" s="0" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H34" s="10"/>
-      <c r="I34" s="10"/>
+      <c r="B34" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="C34" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="D34" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E34" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" s="0" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="B35" s="19" t="n">
-        <v>20</v>
-      </c>
-      <c r="C35" s="19" t="n">
-        <v>70</v>
-      </c>
-      <c r="D35" s="19" t="n">
-        <v>22</v>
-      </c>
-      <c r="E35" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F35" s="20" t="n">
-        <f aca="false">SUM(B35:E35)/12</f>
-        <v>9.33333333333333</v>
-      </c>
-      <c r="G35" s="18" t="n">
-        <f aca="false">SUM(B35:E35)*5</f>
-        <v>560</v>
-      </c>
+      <c r="H35" s="10"/>
+      <c r="I35" s="10"/>
     </row>
     <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="5" t="s">
         <v>59</v>
       </c>
       <c r="B36" s="19" t="n">
-        <v>35.45</v>
+        <v>20</v>
       </c>
       <c r="C36" s="19" t="n">
-        <v>162.02</v>
+        <v>70</v>
       </c>
       <c r="D36" s="19" t="n">
-        <v>83.42</v>
+        <v>22</v>
       </c>
       <c r="E36" s="19" t="n">
-        <v>37.64</v>
-      </c>
-      <c r="F36" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F36" s="18" t="n">
         <f aca="false">SUM(B36:E36)/12</f>
-        <v>26.5441666666667</v>
+        <v>9.33333333333333</v>
       </c>
       <c r="G36" s="18" t="n">
         <f aca="false">SUM(B36:E36)*5</f>
-        <v>1592.65</v>
+        <v>560</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5197,24 +5182,24 @@
         <v>59</v>
       </c>
       <c r="B37" s="19" t="n">
-        <v>18</v>
+        <v>35.45</v>
       </c>
       <c r="C37" s="19" t="n">
-        <v>80</v>
+        <v>162.02</v>
       </c>
       <c r="D37" s="19" t="n">
-        <v>40</v>
+        <v>83.42</v>
       </c>
       <c r="E37" s="19" t="n">
-        <v>18</v>
-      </c>
-      <c r="F37" s="20" t="n">
+        <v>37.64</v>
+      </c>
+      <c r="F37" s="18" t="n">
         <f aca="false">SUM(B37:E37)/12</f>
-        <v>13</v>
+        <v>26.5441666666667</v>
       </c>
       <c r="G37" s="18" t="n">
         <f aca="false">SUM(B37:E37)*5</f>
-        <v>780</v>
+        <v>1592.65</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5222,24 +5207,24 @@
         <v>59</v>
       </c>
       <c r="B38" s="19" t="n">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="C38" s="19" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="D38" s="19" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="E38" s="19" t="n">
-        <v>5</v>
-      </c>
-      <c r="F38" s="20" t="n">
+        <v>18</v>
+      </c>
+      <c r="F38" s="18" t="n">
         <f aca="false">SUM(B38:E38)/12</f>
-        <v>14.5833333333333</v>
+        <v>13</v>
       </c>
       <c r="G38" s="18" t="n">
         <f aca="false">SUM(B38:E38)*5</f>
-        <v>875</v>
+        <v>780</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5247,23 +5232,48 @@
         <v>59</v>
       </c>
       <c r="B39" s="19" t="n">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="C39" s="19" t="n">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="D39" s="19" t="n">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="E39" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="F39" s="20" t="n">
+        <v>5</v>
+      </c>
+      <c r="F39" s="18" t="n">
         <f aca="false">SUM(B39:E39)/12</f>
-        <v>12.1666666666667</v>
+        <v>14.5833333333333</v>
       </c>
       <c r="G39" s="18" t="n">
         <f aca="false">SUM(B39:E39)*5</f>
+        <v>875</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="B40" s="19" t="n">
+        <v>19</v>
+      </c>
+      <c r="C40" s="19" t="n">
+        <v>82</v>
+      </c>
+      <c r="D40" s="19" t="n">
+        <v>43</v>
+      </c>
+      <c r="E40" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="F40" s="18" t="n">
+        <f aca="false">SUM(B40:E40)/12</f>
+        <v>12.1666666666667</v>
+      </c>
+      <c r="G40" s="18" t="n">
+        <f aca="false">SUM(B40:E40)*5</f>
         <v>730</v>
       </c>
     </row>
@@ -5284,10 +5294,10 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:H1048576"/>
-  <sheetFormatPr defaultColWidth="11.70703125" defaultRowHeight="13" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.72265625" defaultRowHeight="13" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="40.5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="19.1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="19.11"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="15.15"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="15"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="15.83"/>
@@ -5312,7 +5322,7 @@
         <v>62</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5379,7 +5389,7 @@
         <v>71</v>
       </c>
       <c r="E10" s="0" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5387,16 +5397,16 @@
         <v>72</v>
       </c>
       <c r="B11" s="0" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="C11" s="0" t="s">
         <v>74</v>
       </c>
       <c r="D11" s="0" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="E11" s="0" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5404,16 +5414,16 @@
         <v>76</v>
       </c>
       <c r="B12" s="0" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="C12" s="0" t="s">
         <v>74</v>
       </c>
       <c r="D12" s="0" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="E12" s="0" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5540,7 +5550,7 @@
         <v>89</v>
       </c>
       <c r="C30" s="0" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5711,7 +5721,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:I46"/>
-  <sheetFormatPr defaultColWidth="12.046875" defaultRowHeight="13" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="12.06640625" defaultRowHeight="13" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="40.5"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="0" width="17.83"/>
@@ -5795,7 +5805,7 @@
         <v>13</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>16</v>
@@ -5815,7 +5825,7 @@
         <v>20</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5823,13 +5833,13 @@
         <v>23</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C14" s="0" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="D14" s="0" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>28</v>
@@ -5877,13 +5887,13 @@
         <v>35</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="D17" s="8" t="s">
         <v>129</v>
       </c>
       <c r="E17" s="9" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5950,7 +5960,7 @@
         <v>20</v>
       </c>
       <c r="F23" s="6" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="G23" s="0" t="s">
         <v>47</v>
@@ -5964,7 +5974,7 @@
         <v>49</v>
       </c>
       <c r="C26" s="0" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6010,7 +6020,7 @@
       <c r="C30" s="0" t="n">
         <v>0.2</v>
       </c>
-      <c r="D30" s="21" t="n">
+      <c r="D30" s="20" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6175,7 +6185,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:H47"/>
-  <sheetFormatPr defaultColWidth="11.70703125" defaultRowHeight="13" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.72265625" defaultRowHeight="13" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="40.5"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="17.67"/>
@@ -6203,7 +6213,7 @@
         <v>62</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6261,16 +6271,16 @@
         <v>69</v>
       </c>
       <c r="B10" s="0" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="C10" s="0" t="s">
         <v>13</v>
       </c>
       <c r="D10" s="0" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="E10" s="0" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6287,7 +6297,7 @@
         <v>75</v>
       </c>
       <c r="E11" s="0" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6304,7 +6314,7 @@
         <v>75</v>
       </c>
       <c r="E12" s="0" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6568,7 +6578,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:C22"/>
-  <sheetFormatPr defaultColWidth="12.046875" defaultRowHeight="13" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="12.06640625" defaultRowHeight="13" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="40.5"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="0" width="78.65"/>
@@ -6577,21 +6587,21 @@
   <sheetData>
     <row r="1" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="0" t="s">
-        <v>153</v>
-      </c>
-      <c r="B1" s="22" t="s">
-        <v>154</v>
+        <v>155</v>
+      </c>
+      <c r="B1" s="21" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="B2" s="0" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="C2" s="0" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6599,7 +6609,7 @@
         <v>62</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6607,7 +6617,7 @@
         <v>64</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6615,7 +6625,7 @@
         <v>65</v>
       </c>
       <c r="B5" s="0" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6623,7 +6633,7 @@
         <v>66</v>
       </c>
       <c r="B6" s="0" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6631,7 +6641,7 @@
         <v>67</v>
       </c>
       <c r="B7" s="0" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6639,7 +6649,7 @@
         <v>17</v>
       </c>
       <c r="B8" s="0" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6647,7 +6657,7 @@
         <v>23</v>
       </c>
       <c r="B9" s="0" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6655,7 +6665,7 @@
         <v>29</v>
       </c>
       <c r="B10" s="0" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6663,7 +6673,7 @@
         <v>32</v>
       </c>
       <c r="B11" s="0" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6671,7 +6681,7 @@
         <v>33</v>
       </c>
       <c r="B12" s="0" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6679,7 +6689,7 @@
         <v>37</v>
       </c>
       <c r="B13" s="0" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6687,15 +6697,15 @@
         <v>48</v>
       </c>
       <c r="B14" s="0" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="0" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="B15" s="0" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6703,7 +6713,7 @@
         <v>50</v>
       </c>
       <c r="B16" s="0" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6711,7 +6721,7 @@
         <v>59</v>
       </c>
       <c r="B17" s="0" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6719,7 +6729,7 @@
         <v>59</v>
       </c>
       <c r="B18" s="0" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6727,7 +6737,7 @@
         <v>59</v>
       </c>
       <c r="B19" s="0" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6735,7 +6745,7 @@
         <v>58</v>
       </c>
       <c r="B20" s="0" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6743,7 +6753,7 @@
         <v>58</v>
       </c>
       <c r="B21" s="0" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6751,7 +6761,7 @@
         <v>58</v>
       </c>
       <c r="B22" s="0" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
   </sheetData>
